--- a/OpenMC_STAR_Model/TBR's.xlsx
+++ b/OpenMC_STAR_Model/TBR's.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rocco698/Desktop/Undergrad/Spring_2026/NUCE_431W/NUCE_431W/OpenMC_STAR_Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{878D8CFE-8507-C446-9345-141578531E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{614CD86B-93E0-444B-9B4E-B70BA37C1B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" xr2:uid="{19FD8DC0-BE1F-DA49-9BCD-F45CFD8ECFC9}"/>
+    <workbookView minimized="1" xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" xr2:uid="{19FD8DC0-BE1F-DA49-9BCD-F45CFD8ECFC9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,6 +33,20 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+  <si>
+    <t>Material</t>
+  </si>
+  <si>
+    <t>(n,t)</t>
+  </si>
+  <si>
+    <t>PbLi (nat.)</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -402,9 +416,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21FEB923-94CE-9048-A235-5E054F03F29C}">
-  <dimension ref="A1"/>
+  <dimension ref="A2:B3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <sheetData>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>0.42057800000000001</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/OpenMC_STAR_Model/TBR's.xlsx
+++ b/OpenMC_STAR_Model/TBR's.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rocco698/Desktop/Undergrad/Spring_2026/NUCE_431W/NUCE_431W/OpenMC_STAR_Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{614CD86B-93E0-444B-9B4E-B70BA37C1B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0461AA94-25D9-C348-B045-7CB502B5C13F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" xr2:uid="{19FD8DC0-BE1F-DA49-9BCD-F45CFD8ECFC9}"/>
+    <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" xr2:uid="{19FD8DC0-BE1F-DA49-9BCD-F45CFD8ECFC9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,15 +36,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
-  <si>
-    <t>Material</t>
-  </si>
-  <si>
-    <t>(n,t)</t>
-  </si>
-  <si>
-    <t>PbLi (nat.)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="9">
+  <si>
+    <t>Particles</t>
+  </si>
+  <si>
+    <t>at % Li</t>
+  </si>
+  <si>
+    <t>FLiBe</t>
+  </si>
+  <si>
+    <t>10K</t>
+  </si>
+  <si>
+    <t>TBR (n,Xt)</t>
+  </si>
+  <si>
+    <t>Margin</t>
+  </si>
+  <si>
+    <t>PbLi (Natural Li, 9.5 gcc)</t>
+  </si>
+  <si>
+    <t>FLiNaK</t>
+  </si>
+  <si>
+    <t>Density (g/cc)</t>
   </si>
 </sst>
 </file>
@@ -80,8 +98,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -416,23 +435,122 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21FEB923-94CE-9048-A235-5E054F03F29C}">
-  <dimension ref="A2:B3"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
       </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" t="s">
+        <v>4</v>
+      </c>
+      <c r="M2" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3">
-        <v>0.42057800000000001</v>
+        <v>0.17</v>
+      </c>
+      <c r="C3">
+        <v>0.44600200000000001</v>
+      </c>
+      <c r="D3">
+        <v>1.4223599999999999E-3</v>
+      </c>
+      <c r="E3">
+        <v>9.5</v>
+      </c>
+      <c r="G3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>1.0445199999999999</v>
+      </c>
+      <c r="I3">
+        <v>3.1094999999999999E-3</v>
+      </c>
+      <c r="K3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>0.86896099999999998</v>
+      </c>
+      <c r="M3">
+        <v>3.05902E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="C4">
+        <v>1.0500100000000001</v>
+      </c>
+      <c r="D4">
+        <v>2.3920299999999999E-3</v>
+      </c>
+      <c r="E4">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1.0569999999999999</v>
+      </c>
+      <c r="D5">
+        <v>2.09756E-3</v>
+      </c>
+      <c r="E5">
+        <v>0.51200000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/OpenMC_STAR_Model/TBR's.xlsx
+++ b/OpenMC_STAR_Model/TBR's.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rocco698/Desktop/Undergrad/Spring_2026/NUCE_431W/NUCE_431W/OpenMC_STAR_Model/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Leaft\Desktop\Temp. Hw\Capstone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0461AA94-25D9-C348-B045-7CB502B5C13F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FAFA160-5C68-4090-9105-C6B3D1151ADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" xr2:uid="{19FD8DC0-BE1F-DA49-9BCD-F45CFD8ECFC9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{19FD8DC0-BE1F-DA49-9BCD-F45CFD8ECFC9}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Material" sheetId="1" r:id="rId1"/>
+    <sheet name="Geometry" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="17">
   <si>
     <t>Particles</t>
   </si>
@@ -63,6 +64,30 @@
   </si>
   <si>
     <t>Density (g/cc)</t>
+  </si>
+  <si>
+    <t>TBR:</t>
+  </si>
+  <si>
+    <t>Plasma--&gt;Pb/Li</t>
+  </si>
+  <si>
+    <t>SteelInCoil--&gt;Plasma--&gt;Pb/Li</t>
+  </si>
+  <si>
+    <t>Pb(83 at%)/Li(17 at%)</t>
+  </si>
+  <si>
+    <t>Plasma--&gt;Pb--&gt;Li *</t>
+  </si>
+  <si>
+    <t>Plasma--&gt;Li--&gt;Pb*</t>
+  </si>
+  <si>
+    <t>Plasma--&gt;Li</t>
+  </si>
+  <si>
+    <t>(density: 0.512 g/cm^3)</t>
   </si>
 </sst>
 </file>
@@ -86,9 +111,18 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top/>
       <bottom/>
@@ -98,9 +132,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -436,9 +471,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21FEB923-94CE-9048-A235-5E054F03F29C}">
   <dimension ref="A1:M5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -449,7 +484,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -484,7 +519,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -519,7 +554,7 @@
         <v>3.05902E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -536,7 +571,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -551,6 +586,72 @@
       </c>
       <c r="E5">
         <v>0.51200000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95316306-EFB9-4052-9201-767301A3C05F}">
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="8.796875" style="2"/>
+    <col min="4" max="4" width="8.796875" style="2"/>
+    <col min="6" max="6" width="8.796875" style="2"/>
+    <col min="7" max="7" width="9.19921875" customWidth="1"/>
+    <col min="8" max="8" width="8.796875" style="2"/>
+    <col min="11" max="11" width="8.796875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0.44600000000000001</v>
+      </c>
+      <c r="I2">
+        <v>0.44500000000000001</v>
+      </c>
+      <c r="K2" s="2">
+        <v>1.0569999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/OpenMC_STAR_Model/TBR's.xlsx
+++ b/OpenMC_STAR_Model/TBR's.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Leaft\Desktop\Temp. Hw\Capstone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FAFA160-5C68-4090-9105-C6B3D1151ADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2BCF699-029F-49BA-A9CE-3EB09102720A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{19FD8DC0-BE1F-DA49-9BCD-F45CFD8ECFC9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{19FD8DC0-BE1F-DA49-9BCD-F45CFD8ECFC9}"/>
   </bookViews>
   <sheets>
     <sheet name="Material" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="24">
   <si>
     <t>Particles</t>
   </si>
@@ -88,6 +88,27 @@
   </si>
   <si>
     <t>(density: 0.512 g/cm^3)</t>
+  </si>
+  <si>
+    <t>Li4SiO4</t>
+  </si>
+  <si>
+    <t>Li8ZrO6</t>
+  </si>
+  <si>
+    <t>Li2O</t>
+  </si>
+  <si>
+    <t>LiAlO2</t>
+  </si>
+  <si>
+    <t>Li5AlO4</t>
+  </si>
+  <si>
+    <t>Li2ZrO3</t>
+  </si>
+  <si>
+    <t>Li2TiO3</t>
   </si>
 </sst>
 </file>
@@ -111,7 +132,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -128,14 +149,93 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -470,10 +570,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21FEB923-94CE-9048-A235-5E054F03F29C}">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -483,8 +583,13 @@
       <c r="K1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="5"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -518,8 +623,17 @@
       <c r="M2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -553,8 +667,11 @@
       <c r="M3">
         <v>3.05902E-3</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O3" s="2"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="7"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -570,8 +687,13 @@
       <c r="E4">
         <v>10.5</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="5"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -587,6 +709,135 @@
       <c r="E5">
         <v>0.51200000000000001</v>
       </c>
+      <c r="O5" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="P5" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O6" s="8"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="10"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="5"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O8" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="P8" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O9" s="8"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="10"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="5"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O11" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="P11" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q11" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O12" s="8"/>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="10"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="5"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O14" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="P14" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O15" s="8"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="10"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="5"/>
+    </row>
+    <row r="17" spans="15:17" x14ac:dyDescent="0.3">
+      <c r="O17" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="P17" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="15:17" x14ac:dyDescent="0.3">
+      <c r="O18" s="8"/>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="10"/>
+    </row>
+    <row r="19" spans="15:17" x14ac:dyDescent="0.3">
+      <c r="O19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="5"/>
+    </row>
+    <row r="20" spans="15:17" x14ac:dyDescent="0.3">
+      <c r="O20" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="P20" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="15:17" x14ac:dyDescent="0.3">
+      <c r="O21" s="8"/>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/OpenMC_STAR_Model/TBR's.xlsx
+++ b/OpenMC_STAR_Model/TBR's.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Leaft\Desktop\Temp. Hw\Capstone\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rocco698/Desktop/Undergrad/Spring_2026/NUCE_431W/NUCE_431W/OpenMC_STAR_Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2BCF699-029F-49BA-A9CE-3EB09102720A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E0ADD66-87CA-E544-9681-F872AE0106B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{19FD8DC0-BE1F-DA49-9BCD-F45CFD8ECFC9}"/>
+    <workbookView xWindow="160" yWindow="920" windowWidth="29920" windowHeight="17280" xr2:uid="{19FD8DC0-BE1F-DA49-9BCD-F45CFD8ECFC9}"/>
   </bookViews>
   <sheets>
     <sheet name="Material" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="26">
   <si>
     <t>Particles</t>
   </si>
@@ -109,13 +109,19 @@
   </si>
   <si>
     <t>Li2TiO3</t>
+  </si>
+  <si>
+    <t>density</t>
+  </si>
+  <si>
+    <t>(nat. Li)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -123,16 +129,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -191,53 +210,37 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF7F7F7F"/>
       </left>
-      <right/>
-      <top/>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Calculation" xfId="1" builtinId="22"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -570,10 +573,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21FEB923-94CE-9048-A235-5E054F03F29C}">
-  <dimension ref="A1:Q21"/>
-  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:R21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -586,10 +589,12 @@
       <c r="O1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P1" s="4"/>
+      <c r="P1" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="Q1" s="5"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -626,14 +631,17 @@
       <c r="O2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="P2" t="s">
         <v>4</v>
       </c>
-      <c r="Q2" s="7" t="s">
+      <c r="Q2" s="6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R2" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -667,11 +675,20 @@
       <c r="M3">
         <v>3.05902E-3</v>
       </c>
-      <c r="O3" s="2"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="7"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O3" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="P3" s="8">
+        <v>0.89361299999999999</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>3.06895E-3</v>
+      </c>
+      <c r="R3" s="8">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -693,7 +710,7 @@
       <c r="P4" s="4"/>
       <c r="Q4" s="5"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -712,132 +729,204 @@
       <c r="O5" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="P5" s="6" t="s">
+      <c r="P5" t="s">
         <v>4</v>
       </c>
-      <c r="Q5" s="7" t="s">
+      <c r="Q5" s="6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="O6" s="8"/>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="10"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R5" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="O6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="P6" s="8">
+        <v>1.0584899999999999</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>3.0057999999999999E-3</v>
+      </c>
+      <c r="R6" s="8">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="O7" s="3" t="s">
         <v>19</v>
       </c>
       <c r="P7" s="4"/>
       <c r="Q7" s="5"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="O8" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="P8" s="6" t="s">
+      <c r="P8" t="s">
         <v>4</v>
       </c>
-      <c r="Q8" s="7" t="s">
+      <c r="Q8" s="6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="O9" s="8"/>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="10"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="O9" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="8">
+        <v>1.2262500000000001</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>2.5111700000000001E-3</v>
+      </c>
+      <c r="R9" s="8">
+        <v>2.0129999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="O10" s="3" t="s">
         <v>20</v>
       </c>
       <c r="P10" s="4"/>
       <c r="Q10" s="5"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="O11" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="P11" s="6" t="s">
+      <c r="P11" t="s">
         <v>4</v>
       </c>
-      <c r="Q11" s="7" t="s">
+      <c r="Q11" s="6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="O12" s="8"/>
-      <c r="P12" s="9"/>
-      <c r="Q12" s="10"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="O12" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="8">
+        <v>0.69713599999999998</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>2.8363199999999998E-3</v>
+      </c>
+      <c r="R12" s="8">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="O13" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P13" s="4"/>
       <c r="Q13" s="5"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="O14" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="P14" s="6" t="s">
+      <c r="P14" t="s">
         <v>4</v>
       </c>
-      <c r="Q14" s="7" t="s">
+      <c r="Q14" s="6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="O15" s="8"/>
-      <c r="P15" s="9"/>
-      <c r="Q15" s="10"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="O15" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="P15" s="8">
+        <v>0.98226999999999998</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>3.8548100000000002E-3</v>
+      </c>
+      <c r="R15" s="8">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="O16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="P16" s="4"/>
       <c r="Q16" s="5"/>
     </row>
-    <row r="17" spans="15:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="15:18" x14ac:dyDescent="0.2">
       <c r="O17" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="P17" s="6" t="s">
+      <c r="P17" t="s">
         <v>4</v>
       </c>
-      <c r="Q17" s="7" t="s">
+      <c r="Q17" s="6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="15:17" x14ac:dyDescent="0.3">
-      <c r="O18" s="8"/>
-      <c r="P18" s="9"/>
-      <c r="Q18" s="10"/>
-    </row>
-    <row r="19" spans="15:17" x14ac:dyDescent="0.3">
+      <c r="R17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="15:18" x14ac:dyDescent="0.2">
+      <c r="O18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="8">
+        <v>0.93399699999999997</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>2.8539099999999999E-3</v>
+      </c>
+      <c r="R18" s="8">
+        <v>4.1500000000000004</v>
+      </c>
+    </row>
+    <row r="19" spans="15:18" x14ac:dyDescent="0.2">
       <c r="O19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="P19" s="4"/>
       <c r="Q19" s="5"/>
     </row>
-    <row r="20" spans="15:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="15:18" x14ac:dyDescent="0.2">
       <c r="O20" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="P20" s="6" t="s">
+      <c r="P20" t="s">
         <v>4</v>
       </c>
-      <c r="Q20" s="7" t="s">
+      <c r="Q20" s="6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="15:17" x14ac:dyDescent="0.3">
-      <c r="O21" s="8"/>
-      <c r="P21" s="9"/>
-      <c r="Q21" s="10"/>
+      <c r="R20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="15:18" x14ac:dyDescent="0.2">
+      <c r="O21" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="8">
+        <v>0.89149800000000001</v>
+      </c>
+      <c r="Q21" s="8">
+        <v>2.0768200000000001E-3</v>
+      </c>
+      <c r="R21" s="8">
+        <v>3.43</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -847,17 +936,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95316306-EFB9-4052-9201-767301A3C05F}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="8.796875" style="2"/>
-    <col min="4" max="4" width="8.796875" style="2"/>
-    <col min="6" max="6" width="8.796875" style="2"/>
-    <col min="7" max="7" width="9.19921875" customWidth="1"/>
-    <col min="8" max="8" width="8.796875" style="2"/>
-    <col min="11" max="11" width="8.796875" style="2"/>
+    <col min="2" max="2" width="8.83203125" style="2"/>
+    <col min="4" max="4" width="8.83203125" style="2"/>
+    <col min="6" max="6" width="8.83203125" style="2"/>
+    <col min="7" max="7" width="9.1640625" customWidth="1"/>
+    <col min="8" max="8" width="8.83203125" style="2"/>
+    <col min="11" max="11" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
         <v>13</v>
       </c>
@@ -874,7 +963,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -894,7 +983,7 @@
         <v>1.0569999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="F3" s="2" t="s">
         <v>12</v>
       </c>

--- a/OpenMC_STAR_Model/TBR's.xlsx
+++ b/OpenMC_STAR_Model/TBR's.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rocco698/Desktop/Undergrad/Spring_2026/NUCE_431W/NUCE_431W/OpenMC_STAR_Model/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\spdai\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E0ADD66-87CA-E544-9681-F872AE0106B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C1D9E46-34AB-435B-A742-3719EB15CDE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="920" windowWidth="29920" windowHeight="17280" xr2:uid="{19FD8DC0-BE1F-DA49-9BCD-F45CFD8ECFC9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{19FD8DC0-BE1F-DA49-9BCD-F45CFD8ECFC9}"/>
   </bookViews>
   <sheets>
     <sheet name="Material" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="27">
   <si>
     <t>Particles</t>
   </si>
@@ -116,6 +116,9 @@
   <si>
     <t>(nat. Li)</t>
   </si>
+  <si>
+    <t>PbLi (92% Enriched Li, 9.5 gcc)</t>
+  </si>
 </sst>
 </file>
 
@@ -138,7 +141,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -150,8 +153,14 @@
         <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -223,21 +232,134 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Calculation" xfId="1" builtinId="22"/>
@@ -254,6 +376,2132 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>TBR of PbLi (Natural Li)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>PbLi</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Material!$B$3:$B$12</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0" formatCode="General">
+                  <c:v>0.17</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="General">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Material!$C$3:$C$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0.44600200000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0500100000000001</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.0569999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B64D-49E2-8E14-E256A5223833}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1188498079"/>
+        <c:axId val="1188498559"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1188498079"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>%</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> Li of mix</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1188498559"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1188498559"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>TBR</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> value</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1188498079"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>TBR of PbLi (Natural Li)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Material!$B$15:$B$23</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0" formatCode="General">
+                  <c:v>0.17</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Material!$C$15:$C$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9435-4516-8FFC-144D6D67681B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1188498079"/>
+        <c:axId val="1188498559"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1188498079"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>%</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> Li of mix</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1188498559"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1188498559"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>TBR</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> value</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1188498079"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>3175</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>666750</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>184150</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F1A076C-7A14-94E0-3C11-D9FF583D9963}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>679450</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0AECA044-0803-4CD3-BD57-703649717F45}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -573,41 +2821,48 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21FEB923-94CE-9048-A235-5E054F03F29C}">
-  <dimension ref="A1:R21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:R24"/>
+  <sheetFormatPr defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="5" max="5" width="11.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A1" s="16" t="s">
         <v>6</v>
       </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="18"/>
       <c r="G1" t="s">
         <v>2</v>
       </c>
       <c r="K1" t="s">
         <v>7</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="Q1" s="5"/>
+      <c r="Q1" s="4"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="10" t="s">
         <v>8</v>
       </c>
       <c r="G2" t="s">
@@ -628,33 +2883,33 @@
       <c r="M2" t="s">
         <v>5</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="P2" t="s">
         <v>4</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="Q2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="R2" s="7" t="s">
+      <c r="R2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A3" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="15">
         <v>0.17</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="12">
         <v>0.44600200000000001</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="15">
         <v>1.4223599999999999E-3</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="13">
         <v>9.5</v>
       </c>
       <c r="G3" t="s">
@@ -675,322 +2930,508 @@
       <c r="M3">
         <v>3.05902E-3</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="P3" s="8">
+      <c r="P3" s="6">
         <v>0.89361299999999999</v>
       </c>
-      <c r="Q3" s="8">
+      <c r="Q3" s="6">
         <v>3.06895E-3</v>
       </c>
-      <c r="R3" s="8">
+      <c r="R3" s="6">
         <v>2.39</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A4" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="C4">
-        <v>1.0500100000000001</v>
-      </c>
-      <c r="D4">
-        <v>2.3920299999999999E-3</v>
-      </c>
-      <c r="E4">
-        <v>10.5</v>
-      </c>
-      <c r="O4" s="3" t="s">
+      <c r="B4" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="C4" s="21"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="22"/>
+      <c r="O4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="5"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="4"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A5" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1.0569999999999999</v>
-      </c>
-      <c r="D5">
-        <v>2.09756E-3</v>
-      </c>
-      <c r="E5">
-        <v>0.51200000000000001</v>
-      </c>
-      <c r="O5" s="2" t="s">
+      <c r="B5" s="26">
+        <v>0.3</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="5"/>
+      <c r="O5" s="1" t="s">
         <v>0</v>
       </c>
       <c r="P5" t="s">
         <v>4</v>
       </c>
-      <c r="Q5" s="6" t="s">
+      <c r="Q5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="R5" s="7" t="s">
+      <c r="R5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="O6" s="8" t="s">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A6" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="P6" s="8">
+      <c r="B6" s="23">
+        <v>0.4</v>
+      </c>
+      <c r="C6" s="21">
+        <v>1.0500100000000001</v>
+      </c>
+      <c r="D6" s="20">
+        <v>2.3920299999999999E-3</v>
+      </c>
+      <c r="E6" s="22">
+        <v>10.5</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="P6" s="6">
         <v>1.0584899999999999</v>
       </c>
-      <c r="Q6" s="8">
+      <c r="Q6" s="6">
         <v>3.0057999999999999E-3</v>
       </c>
-      <c r="R6" s="8">
+      <c r="R6" s="6">
         <v>2.58</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="O7" s="3" t="s">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A7" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="23">
+        <v>0.5</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="5"/>
+      <c r="O7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="5"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="4"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="O8" s="2" t="s">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A8" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="26">
+        <v>0.6</v>
+      </c>
+      <c r="C8" s="21"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="22"/>
+      <c r="O8" s="1" t="s">
         <v>0</v>
       </c>
       <c r="P8" t="s">
         <v>4</v>
       </c>
-      <c r="Q8" s="6" t="s">
+      <c r="Q8" s="5" t="s">
         <v>5</v>
       </c>
       <c r="R8" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="O9" s="8" t="s">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="P9" s="8">
+      <c r="B9" s="23">
+        <v>0.7</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="5"/>
+      <c r="O9" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="6">
         <v>1.2262500000000001</v>
       </c>
-      <c r="Q9" s="8">
+      <c r="Q9" s="6">
         <v>2.5111700000000001E-3</v>
       </c>
-      <c r="R9" s="8">
+      <c r="R9" s="6">
         <v>2.0129999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="O10" s="3" t="s">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A10" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="23">
+        <v>0.8</v>
+      </c>
+      <c r="C10" s="21"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="22"/>
+      <c r="O10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="5"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="4"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="O11" s="2" t="s">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A11" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="26">
+        <v>0.9</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="5"/>
+      <c r="O11" s="1" t="s">
         <v>0</v>
       </c>
       <c r="P11" t="s">
         <v>4</v>
       </c>
-      <c r="Q11" s="6" t="s">
+      <c r="Q11" s="5" t="s">
         <v>5</v>
       </c>
       <c r="R11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="O12" s="8" t="s">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A12" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="P12" s="8">
+      <c r="B12" s="20">
+        <v>1</v>
+      </c>
+      <c r="C12" s="21">
+        <v>1.0569999999999999</v>
+      </c>
+      <c r="D12" s="20">
+        <v>2.09756E-3</v>
+      </c>
+      <c r="E12" s="22">
+        <v>0.51200000000000001</v>
+      </c>
+      <c r="O12" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="6">
         <v>0.69713599999999998</v>
       </c>
-      <c r="Q12" s="8">
+      <c r="Q12" s="6">
         <v>2.8363199999999998E-3</v>
       </c>
-      <c r="R12" s="8">
+      <c r="R12" s="6">
         <v>2.62</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="O13" s="3" t="s">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A13" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="18"/>
+      <c r="O13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="5"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="4"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="O14" s="2" t="s">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A14" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="1" t="s">
         <v>0</v>
       </c>
       <c r="P14" t="s">
         <v>4</v>
       </c>
-      <c r="Q14" s="6" t="s">
+      <c r="Q14" s="5" t="s">
         <v>5</v>
       </c>
       <c r="R14" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="O15" s="8" t="s">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A15" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="P15" s="8">
+      <c r="B15" s="15">
+        <v>0.17</v>
+      </c>
+      <c r="C15" s="12"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="13"/>
+      <c r="O15" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="P15" s="6">
         <v>0.98226999999999998</v>
       </c>
-      <c r="Q15" s="8">
+      <c r="Q15" s="6">
         <v>3.8548100000000002E-3</v>
       </c>
-      <c r="R15" s="8">
+      <c r="R15" s="6">
         <v>2.17</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="O16" s="3" t="s">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A16" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="C16" s="21"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="22"/>
+      <c r="O16" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="P16" s="4"/>
-      <c r="Q16" s="5"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="4"/>
     </row>
-    <row r="17" spans="15:18" x14ac:dyDescent="0.2">
-      <c r="O17" s="2" t="s">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A17" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="26">
+        <v>0.3</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="5"/>
+      <c r="O17" s="1" t="s">
         <v>0</v>
       </c>
       <c r="P17" t="s">
         <v>4</v>
       </c>
-      <c r="Q17" s="6" t="s">
+      <c r="Q17" s="5" t="s">
         <v>5</v>
       </c>
       <c r="R17" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="15:18" x14ac:dyDescent="0.2">
-      <c r="O18" s="8" t="s">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A18" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="8">
+      <c r="B18" s="23">
+        <v>0.4</v>
+      </c>
+      <c r="C18" s="21"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="22"/>
+      <c r="O18" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="6">
         <v>0.93399699999999997</v>
       </c>
-      <c r="Q18" s="8">
+      <c r="Q18" s="6">
         <v>2.8539099999999999E-3</v>
       </c>
-      <c r="R18" s="8">
+      <c r="R18" s="6">
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="19" spans="15:18" x14ac:dyDescent="0.2">
-      <c r="O19" s="3" t="s">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A19" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" s="23">
+        <v>0.5</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="5"/>
+      <c r="O19" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="P19" s="4"/>
-      <c r="Q19" s="5"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="4"/>
     </row>
-    <row r="20" spans="15:18" x14ac:dyDescent="0.2">
-      <c r="O20" s="2" t="s">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A20" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" s="26">
+        <v>0.6</v>
+      </c>
+      <c r="C20" s="21"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="22"/>
+      <c r="O20" s="1" t="s">
         <v>0</v>
       </c>
       <c r="P20" t="s">
         <v>4</v>
       </c>
-      <c r="Q20" s="6" t="s">
+      <c r="Q20" s="5" t="s">
         <v>5</v>
       </c>
       <c r="R20" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="15:18" x14ac:dyDescent="0.2">
-      <c r="O21" s="8" t="s">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A21" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="8">
+      <c r="B21" s="23">
+        <v>0.7</v>
+      </c>
+      <c r="C21" s="7"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="5"/>
+      <c r="O21" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="6">
         <v>0.89149800000000001</v>
       </c>
-      <c r="Q21" s="8">
+      <c r="Q21" s="6">
         <v>2.0768200000000001E-3</v>
       </c>
-      <c r="R21" s="8">
+      <c r="R21" s="6">
         <v>3.43</v>
       </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A22" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" s="23">
+        <v>0.8</v>
+      </c>
+      <c r="C22" s="21"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="22"/>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A23" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" s="26">
+        <v>0.9</v>
+      </c>
+      <c r="C23" s="7"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="5"/>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A24" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24" s="20">
+        <v>1</v>
+      </c>
+      <c r="C24" s="21"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="22"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A13:E13"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95316306-EFB9-4052-9201-767301A3C05F}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="8.83203125" style="2"/>
-    <col min="4" max="4" width="8.83203125" style="2"/>
-    <col min="6" max="6" width="8.83203125" style="2"/>
+    <col min="2" max="2" width="8.83203125" style="1"/>
+    <col min="4" max="4" width="8.83203125" style="1"/>
+    <col min="6" max="6" width="8.83203125" style="1"/>
     <col min="7" max="7" width="9.1640625" customWidth="1"/>
-    <col min="8" max="8" width="8.83203125" style="2"/>
-    <col min="11" max="11" width="8.83203125" style="2"/>
+    <col min="8" max="8" width="8.83203125" style="1"/>
+    <col min="11" max="11" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="1">
         <v>1.6</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="1">
         <v>1.4</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="1">
         <v>0.44600000000000001</v>
       </c>
       <c r="I2">
         <v>0.44500000000000001</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="1">
         <v>1.0569999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="F3" s="2" t="s">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="F3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="1" t="s">
         <v>16</v>
       </c>
     </row>

--- a/OpenMC_STAR_Model/TBR's.xlsx
+++ b/OpenMC_STAR_Model/TBR's.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rocco698/Desktop/Undergrad/Spring_2026/NUCE_431W/NUCE_431W/OpenMC_STAR_Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E0ADD66-87CA-E544-9681-F872AE0106B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2A81CA5-8650-7B47-BCA4-8782B441D27B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="160" yWindow="920" windowWidth="29920" windowHeight="17280" xr2:uid="{19FD8DC0-BE1F-DA49-9BCD-F45CFD8ECFC9}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="30">
   <si>
     <t>Particles</t>
   </si>
@@ -115,16 +115,44 @@
   </si>
   <si>
     <t>(nat. Li)</t>
+  </si>
+  <si>
+    <t>(30% Li-6)</t>
+  </si>
+  <si>
+    <t>(60% Li-6)</t>
+  </si>
+  <si>
+    <t>(90% Li-6)</t>
+  </si>
+  <si>
+    <t>PbLi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -137,8 +165,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -147,11 +183,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -164,46 +216,6 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -223,25 +235,118 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="4"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="3" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="2" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Calculation" xfId="1" builtinId="22"/>
+  <cellStyles count="5">
+    <cellStyle name="Calculation" xfId="3" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="4" builtinId="23"/>
+    <cellStyle name="Heading 4" xfId="1" builtinId="19"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Output" xfId="2" builtinId="21"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -573,10 +678,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21FEB923-94CE-9048-A235-5E054F03F29C}">
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:AG25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:33" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -586,15 +691,32 @@
       <c r="K1" t="s">
         <v>7</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="P1" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q1" s="5"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8"/>
+      <c r="T1" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U1" s="8"/>
+      <c r="V1" s="8"/>
+      <c r="W1" s="8"/>
+      <c r="Y1" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z1" s="8"/>
+      <c r="AA1" s="8"/>
+      <c r="AB1" s="8"/>
+      <c r="AD1" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE1" s="8"/>
+      <c r="AF1" s="8"/>
+      <c r="AG1" s="8"/>
+    </row>
+    <row r="2" spans="1:33" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -628,20 +750,56 @@
       <c r="M2" t="s">
         <v>5</v>
       </c>
-      <c r="O2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="P2" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q2" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="R2" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="O2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG2" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -675,20 +833,44 @@
       <c r="M3">
         <v>3.05902E-3</v>
       </c>
-      <c r="O3" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="P3" s="8">
+      <c r="O3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P3" s="5">
         <v>0.89361299999999999</v>
       </c>
-      <c r="Q3" s="8">
+      <c r="Q3" s="3">
         <v>3.06895E-3</v>
       </c>
-      <c r="R3" s="8">
+      <c r="R3" s="3">
         <v>2.39</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="T3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U3" s="5"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3">
+        <v>2.39</v>
+      </c>
+      <c r="Y3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z3" s="5"/>
+      <c r="AA3" s="3"/>
+      <c r="AB3" s="3">
+        <v>2.39</v>
+      </c>
+      <c r="AD3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE3" s="5"/>
+      <c r="AF3" s="3"/>
+      <c r="AG3" s="3">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -704,13 +886,32 @@
       <c r="E4">
         <v>10.5</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="O4" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="5"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+      <c r="T4" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="U4" s="10"/>
+      <c r="V4" s="10"/>
+      <c r="W4" s="10"/>
+      <c r="Y4" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z4" s="10"/>
+      <c r="AA4" s="10"/>
+      <c r="AB4" s="10"/>
+      <c r="AD4" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE4" s="10"/>
+      <c r="AF4" s="10"/>
+      <c r="AG4" s="10"/>
+    </row>
+    <row r="5" spans="1:33" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -726,209 +927,943 @@
       <c r="E5">
         <v>0.51200000000000001</v>
       </c>
-      <c r="O5" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="P5" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q5" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="R5" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="O6" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="P6" s="8">
+      <c r="O5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="T5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="V5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="W5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG5" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="O6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P6" s="5">
         <v>1.0584899999999999</v>
       </c>
-      <c r="Q6" s="8">
+      <c r="Q6" s="3">
         <v>3.0057999999999999E-3</v>
       </c>
-      <c r="R6" s="8">
+      <c r="R6" s="3">
         <v>2.58</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="O7" s="3" t="s">
+      <c r="T6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U6" s="5"/>
+      <c r="V6" s="3"/>
+      <c r="W6" s="3">
+        <v>2.58</v>
+      </c>
+      <c r="Y6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z6" s="5"/>
+      <c r="AA6" s="3"/>
+      <c r="AB6" s="3">
+        <v>2.58</v>
+      </c>
+      <c r="AD6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE6" s="5"/>
+      <c r="AF6" s="3"/>
+      <c r="AG6" s="3">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="G7" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="O7" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="5"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="O8" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="P8" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q8" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="R8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="O9" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="P9" s="8">
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10"/>
+      <c r="T7" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="U7" s="10"/>
+      <c r="V7" s="10"/>
+      <c r="W7" s="10"/>
+      <c r="Y7" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z7" s="10"/>
+      <c r="AA7" s="10"/>
+      <c r="AB7" s="10"/>
+      <c r="AD7" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE7" s="10"/>
+      <c r="AF7" s="10"/>
+      <c r="AG7" s="10"/>
+    </row>
+    <row r="8" spans="1:33" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="R8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="T8" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="U8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="V8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="W8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y8" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD8" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG8" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="5">
+        <v>1.0445199999999999</v>
+      </c>
+      <c r="I9" s="3">
+        <v>3.1094999999999999E-3</v>
+      </c>
+      <c r="J9" s="3">
+        <v>2</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="5">
         <v>1.2262500000000001</v>
       </c>
-      <c r="Q9" s="8">
+      <c r="Q9" s="3">
         <v>2.5111700000000001E-3</v>
       </c>
-      <c r="R9" s="8">
+      <c r="R9" s="3">
         <v>2.0129999999999999</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="O10" s="3" t="s">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U9" s="5"/>
+      <c r="V9" s="3"/>
+      <c r="W9" s="3">
+        <v>2.0129999999999999</v>
+      </c>
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z9" s="5"/>
+      <c r="AA9" s="3"/>
+      <c r="AB9" s="3">
+        <v>2.0129999999999999</v>
+      </c>
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE9" s="5"/>
+      <c r="AF9" s="3"/>
+      <c r="AG9" s="3">
+        <v>2.0129999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="O10" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="5"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="O11" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="P11" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q11" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="R11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="O12" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="P12" s="8">
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
+      <c r="T10" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="U10" s="10"/>
+      <c r="V10" s="10"/>
+      <c r="W10" s="10"/>
+      <c r="Y10" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z10" s="10"/>
+      <c r="AA10" s="10"/>
+      <c r="AB10" s="10"/>
+      <c r="AD10" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="AE10" s="10"/>
+      <c r="AF10" s="10"/>
+      <c r="AG10" s="10"/>
+    </row>
+    <row r="11" spans="1:33" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="G11" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="O11" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="P11" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q11" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="R11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="T11" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="U11" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="V11" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="W11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y11" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA11" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD11" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF11" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG11" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="G12" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="5">
         <v>0.69713599999999998</v>
       </c>
-      <c r="Q12" s="8">
+      <c r="Q12" s="3">
         <v>2.8363199999999998E-3</v>
       </c>
-      <c r="R12" s="8">
+      <c r="R12" s="3">
         <v>2.62</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="O13" s="3" t="s">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U12" s="5"/>
+      <c r="V12" s="3"/>
+      <c r="W12" s="3">
+        <v>2.62</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z12" s="5"/>
+      <c r="AA12" s="3"/>
+      <c r="AB12" s="3">
+        <v>2.62</v>
+      </c>
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE12" s="5"/>
+      <c r="AF12" s="3"/>
+      <c r="AG12" s="3">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0.86896099999999998</v>
+      </c>
+      <c r="I13" s="3">
+        <v>3.05902E-3</v>
+      </c>
+      <c r="J13" s="3">
+        <v>2</v>
+      </c>
+      <c r="O13" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="5"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="O14" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="P14" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q14" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="R14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="O15" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="P15" s="8">
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="10"/>
+      <c r="T13" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="U13" s="10"/>
+      <c r="V13" s="10"/>
+      <c r="W13" s="10"/>
+      <c r="Y13" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z13" s="10"/>
+      <c r="AA13" s="10"/>
+      <c r="AB13" s="10"/>
+      <c r="AD13" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AE13" s="10"/>
+      <c r="AF13" s="10"/>
+      <c r="AG13" s="10"/>
+    </row>
+    <row r="14" spans="1:33" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="O14" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="P14" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="T14" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="U14" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="V14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="W14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y14" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD14" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG14" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="O15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P15" s="5">
         <v>0.98226999999999998</v>
       </c>
-      <c r="Q15" s="8">
+      <c r="Q15" s="3">
         <v>3.8548100000000002E-3</v>
       </c>
-      <c r="R15" s="8">
+      <c r="R15" s="3">
         <v>2.17</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="O16" s="3" t="s">
+      <c r="T15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U15" s="5"/>
+      <c r="V15" s="3"/>
+      <c r="W15" s="3">
+        <v>2.17</v>
+      </c>
+      <c r="Y15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z15" s="5"/>
+      <c r="AA15" s="3"/>
+      <c r="AB15" s="3">
+        <v>2.17</v>
+      </c>
+      <c r="AD15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE15" s="5"/>
+      <c r="AF15" s="3"/>
+      <c r="AG15" s="3">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="O16" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="P16" s="4"/>
-      <c r="Q16" s="5"/>
-    </row>
-    <row r="17" spans="15:18" x14ac:dyDescent="0.2">
-      <c r="O17" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="P17" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q17" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="R17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="15:18" x14ac:dyDescent="0.2">
-      <c r="O18" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="P18" s="8">
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10"/>
+      <c r="T16" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="U16" s="10"/>
+      <c r="V16" s="10"/>
+      <c r="W16" s="10"/>
+      <c r="Y16" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z16" s="10"/>
+      <c r="AA16" s="10"/>
+      <c r="AB16" s="10"/>
+      <c r="AD16" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE16" s="10"/>
+      <c r="AF16" s="10"/>
+      <c r="AG16" s="10"/>
+    </row>
+    <row r="17" spans="1:33" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="O17" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="P17" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="R17" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="T17" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="U17" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="V17" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="W17" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y17" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA17" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB17" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD17" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF17" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG17" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="5">
         <v>0.93399699999999997</v>
       </c>
-      <c r="Q18" s="8">
+      <c r="Q18" s="3">
         <v>2.8539099999999999E-3</v>
       </c>
-      <c r="R18" s="8">
+      <c r="R18" s="3">
         <v>4.1500000000000004</v>
       </c>
-    </row>
-    <row r="19" spans="15:18" x14ac:dyDescent="0.2">
-      <c r="O19" s="3" t="s">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U18" s="5"/>
+      <c r="V18" s="3"/>
+      <c r="W18" s="3">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z18" s="5"/>
+      <c r="AA18" s="3"/>
+      <c r="AB18" s="3">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE18" s="5"/>
+      <c r="AF18" s="3"/>
+      <c r="AG18" s="3">
+        <v>4.1500000000000004</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="O19" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="P19" s="4"/>
-      <c r="Q19" s="5"/>
-    </row>
-    <row r="20" spans="15:18" x14ac:dyDescent="0.2">
-      <c r="O20" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="P20" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q20" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="R20" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="15:18" x14ac:dyDescent="0.2">
-      <c r="O21" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="8">
+      <c r="P19" s="10"/>
+      <c r="Q19" s="10"/>
+      <c r="R19" s="10"/>
+      <c r="T19" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="U19" s="10"/>
+      <c r="V19" s="10"/>
+      <c r="W19" s="10"/>
+      <c r="Y19" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z19" s="10"/>
+      <c r="AA19" s="10"/>
+      <c r="AB19" s="10"/>
+      <c r="AD19" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE19" s="10"/>
+      <c r="AF19" s="10"/>
+      <c r="AG19" s="10"/>
+    </row>
+    <row r="20" spans="1:33" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="O20" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="P20" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="T20" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="U20" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="V20" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="W20" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y20" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA20" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB20" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD20" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF20" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG20" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="5">
         <v>0.89149800000000001</v>
       </c>
-      <c r="Q21" s="8">
+      <c r="Q21" s="3">
         <v>2.0768200000000001E-3</v>
       </c>
-      <c r="R21" s="8">
+      <c r="R21" s="3">
         <v>3.43</v>
       </c>
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="5"/>
+      <c r="V21" s="3"/>
+      <c r="W21" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z21" s="5"/>
+      <c r="AA21" s="3"/>
+      <c r="AB21" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE21" s="5"/>
+      <c r="AF21" s="3"/>
+      <c r="AG21" s="3">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:33" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="O22" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="P22" s="6"/>
+      <c r="Q22" s="6"/>
+      <c r="R22" s="6"/>
+      <c r="T22" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="U22" s="6"/>
+      <c r="V22" s="6"/>
+      <c r="W22" s="6"/>
+      <c r="Y22" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z22" s="6"/>
+      <c r="AA22" s="6"/>
+      <c r="AB22" s="6"/>
+      <c r="AD22" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE22" s="6"/>
+      <c r="AF22" s="6"/>
+      <c r="AG22" s="6"/>
+    </row>
+    <row r="23" spans="1:33" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:33" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A25" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
     </row>
   </sheetData>
+  <mergeCells count="43">
+    <mergeCell ref="G11:J11"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="AD19:AG19"/>
+    <mergeCell ref="AD22:AG22"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="AD1:AG1"/>
+    <mergeCell ref="AD4:AG4"/>
+    <mergeCell ref="AD7:AG7"/>
+    <mergeCell ref="AD10:AG10"/>
+    <mergeCell ref="AD13:AG13"/>
+    <mergeCell ref="AD16:AG16"/>
+    <mergeCell ref="T19:W19"/>
+    <mergeCell ref="T22:W22"/>
+    <mergeCell ref="Y1:AB1"/>
+    <mergeCell ref="Y4:AB4"/>
+    <mergeCell ref="Y7:AB7"/>
+    <mergeCell ref="Y10:AB10"/>
+    <mergeCell ref="Y13:AB13"/>
+    <mergeCell ref="Y16:AB16"/>
+    <mergeCell ref="Y19:AB19"/>
+    <mergeCell ref="Y22:AB22"/>
+    <mergeCell ref="T1:W1"/>
+    <mergeCell ref="T4:W4"/>
+    <mergeCell ref="T7:W7"/>
+    <mergeCell ref="T10:W10"/>
+    <mergeCell ref="T13:W13"/>
+    <mergeCell ref="T16:W16"/>
+    <mergeCell ref="O22:R22"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="O4:R4"/>
+    <mergeCell ref="O7:R7"/>
+    <mergeCell ref="O10:R10"/>
+    <mergeCell ref="O13:R13"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="O19:R19"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
